--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -672,8 +672,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
+</t>
   </si>
   <si>
     <t>Reported rather than primary record</t>
@@ -839,7 +839,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device)
 </t>
   </si>
   <si>
@@ -858,7 +858,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|RelatedPerson|CareTeam)
 </t>
   </si>
   <si>
@@ -904,7 +904,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -956,7 +956,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -1006,7 +1006,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|MedicationRequest|4.0.1|ServiceRequest|4.0.1|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|ServiceRequest|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1342,7 +1342,7 @@
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1434,7 +1434,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest)
 </t>
   </si>
   <si>
@@ -1815,7 +1815,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
